--- a/data/intermediate/fix.xlsx
+++ b/data/intermediate/fix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8744" uniqueCount="8744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8747" uniqueCount="8747">
   <si>
     <t>fecha</t>
   </si>
@@ -26246,6 +26246,15 @@
   </si>
   <si>
     <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
   </si>
 </sst>
 </file>
@@ -26577,7 +26586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8743"/>
+  <dimension ref="A1:B8746"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -96524,6 +96533,30 @@
         <v>16.9647</v>
       </c>
     </row>
+    <row r="8744" spans="1:2">
+      <c r="A8744" t="s">
+        <v>8744</v>
+      </c>
+      <c r="B8744">
+        <v>16.946</v>
+      </c>
+    </row>
+    <row r="8745" spans="1:2">
+      <c r="A8745" t="s">
+        <v>8745</v>
+      </c>
+      <c r="B8745">
+        <v>16.966</v>
+      </c>
+    </row>
+    <row r="8746" spans="1:2">
+      <c r="A8746" t="s">
+        <v>8746</v>
+      </c>
+      <c r="B8746">
+        <v>16.9712</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/intermediate/fix.xlsx
+++ b/data/intermediate/fix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8747" uniqueCount="8747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8753" uniqueCount="8753">
   <si>
     <t>fecha</t>
   </si>
@@ -26255,6 +26255,24 @@
   </si>
   <si>
     <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
   </si>
 </sst>
 </file>
@@ -26586,7 +26604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8746"/>
+  <dimension ref="A1:B8752"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -96557,6 +96575,54 @@
         <v>16.9712</v>
       </c>
     </row>
+    <row r="8747" spans="1:2">
+      <c r="A8747" t="s">
+        <v>8747</v>
+      </c>
+      <c r="B8747">
+        <v>17.0427</v>
+      </c>
+    </row>
+    <row r="8748" spans="1:2">
+      <c r="A8748" t="s">
+        <v>8748</v>
+      </c>
+      <c r="B8748">
+        <v>17.0147</v>
+      </c>
+    </row>
+    <row r="8749" spans="1:2">
+      <c r="A8749" t="s">
+        <v>8749</v>
+      </c>
+      <c r="B8749">
+        <v>16.9755</v>
+      </c>
+    </row>
+    <row r="8750" spans="1:2">
+      <c r="A8750" t="s">
+        <v>8750</v>
+      </c>
+      <c r="B8750">
+        <v>16.9852</v>
+      </c>
+    </row>
+    <row r="8751" spans="1:2">
+      <c r="A8751" t="s">
+        <v>8751</v>
+      </c>
+      <c r="B8751">
+        <v>16.956</v>
+      </c>
+    </row>
+    <row r="8752" spans="1:2">
+      <c r="A8752" t="s">
+        <v>8752</v>
+      </c>
+      <c r="B8752">
+        <v>16.8748</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
